--- a/Terranor modell.xlsx
+++ b/Terranor modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A5FB71-CAC6-5C46-8A1F-E50DAA1113D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB55F3A-B1DE-8042-9CD2-56388EBA5F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25260" yWindow="500" windowWidth="25940" windowHeight="26740" activeTab="3" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
+    <workbookView xWindow="25220" yWindow="500" windowWidth="24940" windowHeight="26500" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -23,8 +23,6 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">SOTP!$C$7:$C$15</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">SOTP!$G$7:$G$15</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">SOTP!$C$7:$C$15</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">SOTP!$G$7:$G$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="163">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -509,6 +507,33 @@
   </si>
   <si>
     <t>Equity value</t>
+  </si>
+  <si>
+    <t>16.04.26: Terranor vinner to kontrakter verdt SEKm 36 for drenering og ventilasjon på veien i sør-Sverige</t>
+  </si>
+  <si>
+    <t>16.04.26: Terranor vinner kontrakt i Sør-øst Värmland verdt SEKm 214, går fra 1.sep 26 til 31.aug 30</t>
+  </si>
+  <si>
+    <t>17.04.26: Tendersesongen er ferdig og Terranor bekrefter at 6 kontrakter verdt SEKm 251 har utløpt og 6 nye kontrakter har blitt fornyet, verdt SEK 366. Økning på 45%</t>
+  </si>
+  <si>
+    <t>17.04.26: Terranor tildeles to-års opsjon verdt SEKm 175 i Gøteborg</t>
+  </si>
+  <si>
+    <t>24.04.26: Terranor vinner vedlikeholdskontrakt i Järvenpää verdt SEKm 116</t>
+  </si>
+  <si>
+    <t>01.05.26: Terranor vinner kontrakt i Ikast-Brande verdt SEKm 206</t>
+  </si>
+  <si>
+    <t>11.05.26: Terranor vinner kontrakt i Falun verdt SEKm 37</t>
+  </si>
+  <si>
+    <t>18.05.26: Terranor vinner kontrakt i Falun verdt SEKm 36</t>
+  </si>
+  <si>
+    <t>29.06.26: Terranor vinner kontrakt i København verdt SEKm 115. Viktig for srategier til Terr å vinne flere municipalities i Danmark</t>
   </si>
 </sst>
 </file>
@@ -698,7 +723,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -754,7 +779,6 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -785,10 +809,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1472,50 +1496,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>203200</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Bilde 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{396DC847-8D85-9ACA-9CF9-D9FEFBBF91C2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4330700" y="0"/>
-          <a:ext cx="6464300" cy="2717800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>431800</xdr:colOff>
       <xdr:row>0</xdr:row>
@@ -1541,7 +1521,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1963,7 +1943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6FABC2-1253-924E-8CB2-F0C03750A097}">
-  <dimension ref="A5:O38"/>
+  <dimension ref="A5:O47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="10.83203125" style="2"/>
@@ -2000,71 +1980,116 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2235,7 +2260,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="19">
-        <v>30.6</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>43</v>
@@ -2425,7 +2450,7 @@
       </c>
       <c r="B6" s="5">
         <f>B4*B5</f>
-        <v>612</v>
+        <v>680</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>45</v>
@@ -2484,39 +2509,39 @@
         <f>AC4*-0.7</f>
         <v>-2799.5309999999999</v>
       </c>
-      <c r="AD6" s="49">
+      <c r="AD6" s="13">
         <f t="shared" ref="AD6:AL6" si="1">AD4*-0.7</f>
         <v>-3079.4841000000006</v>
       </c>
-      <c r="AE6" s="49">
+      <c r="AE6" s="13">
         <f t="shared" si="1"/>
         <v>-3387.4325100000005</v>
       </c>
-      <c r="AF6" s="49">
+      <c r="AF6" s="13">
         <f t="shared" si="1"/>
         <v>-3556.8041355000005</v>
       </c>
-      <c r="AG6" s="49">
+      <c r="AG6" s="13">
         <f t="shared" si="1"/>
         <v>-3734.6443422750003</v>
       </c>
-      <c r="AH6" s="49">
+      <c r="AH6" s="13">
         <f t="shared" si="1"/>
         <v>-3921.3765593887501</v>
       </c>
-      <c r="AI6" s="49">
+      <c r="AI6" s="13">
         <f t="shared" si="1"/>
         <v>-4117.4453873581879</v>
       </c>
-      <c r="AJ6" s="49">
+      <c r="AJ6" s="13">
         <f t="shared" si="1"/>
         <v>-4323.3176567260971</v>
       </c>
-      <c r="AK6" s="49">
+      <c r="AK6" s="13">
         <f t="shared" si="1"/>
         <v>-4539.4835395624023</v>
       </c>
-      <c r="AL6" s="49">
+      <c r="AL6" s="13">
         <f t="shared" si="1"/>
         <v>-4766.4577165405226</v>
       </c>
@@ -2743,7 +2768,7 @@
       </c>
       <c r="B9" s="6">
         <f>B6-B7+B8</f>
-        <v>661.56700000000001</v>
+        <v>729.56700000000001</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>48</v>
@@ -4032,7 +4057,7 @@
         <v>67.505526451694593</v>
       </c>
     </row>
-    <row r="17" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="C17" s="2" t="s">
         <v>56</v>
       </c>
@@ -4130,7 +4155,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="C18" s="2" t="s">
         <v>57</v>
       </c>
@@ -4259,7 +4284,7 @@
         <v>12.218121073063852</v>
       </c>
     </row>
-    <row r="19" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
@@ -4287,7 +4312,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
         <v>35</v>
       </c>
@@ -4407,7 +4432,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="21" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="C21" s="2" t="s">
         <v>38</v>
       </c>
@@ -4543,7 +4568,7 @@
         <v>2225.5992977151982</v>
       </c>
     </row>
-    <row r="22" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="C22" s="2" t="s">
         <v>36</v>
       </c>
@@ -4678,7 +4703,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="C23" s="2" t="s">
         <v>139</v>
       </c>
@@ -4716,7 +4741,7 @@
         <v>111.27996488575991</v>
       </c>
     </row>
-    <row r="24" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="M24" s="16"/>
       <c r="P24" s="16"/>
       <c r="Q24" s="16"/>
@@ -4739,10 +4764,10 @@
       </c>
       <c r="AO24" s="22">
         <f>(AO23-B4)/B4</f>
-        <v>2.6366001596653565</v>
-      </c>
-    </row>
-    <row r="25" spans="2:41" x14ac:dyDescent="0.25">
+        <v>2.272940143698821</v>
+      </c>
+    </row>
+    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="C25" s="2" t="s">
         <v>125</v>
       </c>
@@ -4782,7 +4807,7 @@
         <v>176.661</v>
       </c>
     </row>
-    <row r="26" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="C26" s="2" t="s">
         <v>126</v>
       </c>
@@ -4845,7 +4870,7 @@
       <c r="AK26" s="17"/>
       <c r="AL26" s="17"/>
     </row>
-    <row r="27" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
@@ -4872,7 +4897,7 @@
       <c r="AK27" s="17"/>
       <c r="AL27" s="17"/>
     </row>
-    <row r="28" spans="2:41" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="14"/>
       <c r="C28" s="13" t="s">
         <v>119</v>
@@ -4911,16 +4936,16 @@
         <f>AC4*AC29</f>
         <v>155.97387000000001</v>
       </c>
-      <c r="AD28" s="49">
+      <c r="AD28" s="13">
         <f t="shared" ref="AD28:AE28" si="40">AD4*AD29</f>
         <v>197.96683500000003</v>
       </c>
-      <c r="AE28" s="49">
+      <c r="AE28" s="13">
         <f t="shared" si="40"/>
         <v>241.95946500000005</v>
       </c>
     </row>
-    <row r="29" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="C29" s="2" t="s">
         <v>126</v>
       </c>
@@ -4965,7 +4990,7 @@
       <c r="Y29" s="9"/>
       <c r="Z29" s="9"/>
       <c r="AA29" s="9">
-        <f t="shared" ref="Y29:AA29" si="42">AA28/AA4</f>
+        <f t="shared" ref="AA29" si="42">AA28/AA4</f>
         <v>2.8440434607973238E-2</v>
       </c>
       <c r="AB29" s="9">
@@ -4989,7 +5014,7 @@
       <c r="AK29" s="17"/>
       <c r="AL29" s="17"/>
     </row>
-    <row r="31" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="C31" s="1" t="s">
         <v>59</v>
       </c>
@@ -5018,19 +5043,15 @@
       <c r="Z31" s="20"/>
       <c r="AA31" s="20"/>
     </row>
-    <row r="32" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:41" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="4"/>
       <c r="C32" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
       <c r="G32" s="13">
         <v>0</v>
       </c>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
       <c r="K32" s="13">
         <v>0</v>
       </c>
@@ -5061,10 +5082,6 @@
       <c r="T32" s="13">
         <v>18.626000000000001</v>
       </c>
-      <c r="U32" s="13"/>
-      <c r="V32" s="13"/>
-      <c r="W32" s="13"/>
-      <c r="X32" s="13"/>
       <c r="Y32" s="9"/>
       <c r="Z32" s="9"/>
       <c r="AA32" s="13">
@@ -5073,20 +5090,17 @@
       <c r="AB32" s="13">
         <v>18.626000000000001</v>
       </c>
-    </row>
-    <row r="33" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC32" s="14"/>
+    </row>
+    <row r="33" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="4"/>
       <c r="C33" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
       <c r="G33" s="13">
         <v>50.286000000000001</v>
       </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
       <c r="K33" s="13">
         <v>40.090000000000003</v>
       </c>
@@ -5117,10 +5131,6 @@
       <c r="T33" s="13">
         <v>17.024000000000001</v>
       </c>
-      <c r="U33" s="13"/>
-      <c r="V33" s="13"/>
-      <c r="W33" s="13"/>
-      <c r="X33" s="13"/>
       <c r="Y33" s="9"/>
       <c r="Z33" s="9"/>
       <c r="AA33" s="13">
@@ -5129,30 +5139,17 @@
       <c r="AB33" s="13">
         <v>18.827000000000002</v>
       </c>
-      <c r="AC33" s="18"/>
-      <c r="AD33" s="17"/>
-      <c r="AE33" s="17"/>
-      <c r="AF33" s="17"/>
-      <c r="AG33" s="17"/>
-      <c r="AH33" s="17"/>
-      <c r="AI33" s="17"/>
-      <c r="AJ33" s="17"/>
-      <c r="AK33" s="17"/>
-      <c r="AL33" s="17"/>
-    </row>
-    <row r="34" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC33" s="14"/>
+    </row>
+    <row r="34" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="4"/>
       <c r="C34" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
       <c r="G34" s="13">
         <v>76.400000000000006</v>
       </c>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
       <c r="K34" s="13">
         <v>68.822000000000003</v>
       </c>
@@ -5183,10 +5180,6 @@
       <c r="T34" s="13">
         <v>99.933000000000007</v>
       </c>
-      <c r="U34" s="13"/>
-      <c r="V34" s="13"/>
-      <c r="W34" s="13"/>
-      <c r="X34" s="13"/>
       <c r="Y34" s="17"/>
       <c r="Z34" s="17"/>
       <c r="AA34" s="13">
@@ -5195,20 +5188,17 @@
       <c r="AB34" s="13">
         <v>105.441</v>
       </c>
-    </row>
-    <row r="35" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC34" s="14"/>
+    </row>
+    <row r="35" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="4"/>
       <c r="C35" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
       <c r="G35" s="13">
         <v>167.143</v>
       </c>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
       <c r="K35" s="13">
         <v>213.87899999999999</v>
       </c>
@@ -5239,30 +5229,25 @@
       <c r="T35" s="13">
         <v>397.10599999999999</v>
       </c>
-      <c r="U35" s="13"/>
-      <c r="V35" s="13"/>
-      <c r="W35" s="13"/>
-      <c r="X35" s="13"/>
+      <c r="Y35" s="2"/>
+      <c r="Z35" s="2"/>
       <c r="AA35" s="13">
         <v>288.166</v>
       </c>
       <c r="AB35" s="13">
         <v>393.55520000000001</v>
       </c>
-    </row>
-    <row r="36" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC35" s="14"/>
+    </row>
+    <row r="36" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="4"/>
       <c r="C36" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
       <c r="G36" s="13">
         <v>0</v>
       </c>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
       <c r="K36" s="13">
         <v>0</v>
       </c>
@@ -5293,30 +5278,25 @@
       <c r="T36" s="13">
         <v>13.571</v>
       </c>
-      <c r="U36" s="13"/>
-      <c r="V36" s="13"/>
-      <c r="W36" s="13"/>
-      <c r="X36" s="13"/>
+      <c r="Y36" s="2"/>
+      <c r="Z36" s="2"/>
       <c r="AA36" s="13">
         <v>20.6</v>
       </c>
       <c r="AB36" s="13">
         <v>11.711</v>
       </c>
-    </row>
-    <row r="37" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC36" s="14"/>
+    </row>
+    <row r="37" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="4"/>
       <c r="C37" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
       <c r="G37" s="13">
         <v>4.6550000000000002</v>
       </c>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
       <c r="K37" s="13">
         <v>5.5</v>
       </c>
@@ -5347,30 +5327,25 @@
       <c r="T37" s="13">
         <v>4.1379999999999999</v>
       </c>
-      <c r="U37" s="13"/>
-      <c r="V37" s="13"/>
-      <c r="W37" s="13"/>
-      <c r="X37" s="13"/>
+      <c r="Y37" s="2"/>
+      <c r="Z37" s="2"/>
       <c r="AA37" s="13">
         <v>12.2</v>
       </c>
       <c r="AB37" s="13">
         <v>4.1669999999999998</v>
       </c>
-    </row>
-    <row r="38" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC37" s="14"/>
+    </row>
+    <row r="38" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="4"/>
       <c r="C38" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
       <c r="G38" s="13">
         <v>25.591000000000001</v>
       </c>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
       <c r="K38" s="13">
         <v>26.21</v>
       </c>
@@ -5401,30 +5376,25 @@
       <c r="T38" s="13">
         <v>28.867999999999999</v>
       </c>
-      <c r="U38" s="13"/>
-      <c r="V38" s="13"/>
-      <c r="W38" s="13"/>
-      <c r="X38" s="13"/>
+      <c r="Y38" s="2"/>
+      <c r="Z38" s="2"/>
       <c r="AA38" s="13">
         <v>21.38</v>
       </c>
       <c r="AB38" s="13">
         <v>30.613</v>
       </c>
-    </row>
-    <row r="39" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC38" s="14"/>
+    </row>
+    <row r="39" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="4"/>
       <c r="C39" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
       <c r="G39" s="13">
         <v>256.64100000000002</v>
       </c>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
       <c r="K39" s="13">
         <v>398.19200000000001</v>
       </c>
@@ -5455,30 +5425,25 @@
       <c r="T39" s="13">
         <v>251.03700000000001</v>
       </c>
-      <c r="U39" s="13"/>
-      <c r="V39" s="13"/>
-      <c r="W39" s="13"/>
-      <c r="X39" s="13"/>
+      <c r="Y39" s="2"/>
+      <c r="Z39" s="2"/>
       <c r="AA39" s="13">
         <v>369.39299999999997</v>
       </c>
       <c r="AB39" s="13">
         <v>407.06799999999998</v>
       </c>
-    </row>
-    <row r="40" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC39" s="14"/>
+    </row>
+    <row r="40" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="4"/>
       <c r="C40" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
       <c r="G40" s="13">
         <v>102.79600000000001</v>
       </c>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
       <c r="K40" s="13">
         <v>133.49600000000001</v>
       </c>
@@ -5509,30 +5474,25 @@
       <c r="T40" s="13">
         <v>342.72899999999998</v>
       </c>
-      <c r="U40" s="13"/>
-      <c r="V40" s="13"/>
-      <c r="W40" s="13"/>
-      <c r="X40" s="13"/>
+      <c r="Y40" s="2"/>
+      <c r="Z40" s="2"/>
       <c r="AA40" s="13">
         <v>166.1</v>
       </c>
       <c r="AB40" s="13">
         <v>246.11600000000001</v>
       </c>
-    </row>
-    <row r="41" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC40" s="14"/>
+    </row>
+    <row r="41" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="4"/>
       <c r="C41" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
       <c r="G41" s="13">
         <v>43.436999999999998</v>
       </c>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
       <c r="K41" s="13">
         <v>29.334</v>
       </c>
@@ -5563,18 +5523,19 @@
       <c r="T41" s="13">
         <v>32.676000000000002</v>
       </c>
-      <c r="U41" s="13"/>
-      <c r="V41" s="13"/>
-      <c r="W41" s="13"/>
-      <c r="X41" s="13"/>
+      <c r="Y41" s="2"/>
+      <c r="Z41" s="2"/>
       <c r="AA41" s="13">
         <v>45.292000000000002</v>
       </c>
       <c r="AB41" s="13">
         <v>76.736000000000004</v>
       </c>
-    </row>
-    <row r="42" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC41" s="14"/>
+    </row>
+    <row r="42" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="B42" s="4"/>
       <c r="C42" s="1" t="s">
         <v>70</v>
       </c>
@@ -5646,10 +5607,8 @@
         <f t="shared" si="44"/>
         <v>1205.7080000000001</v>
       </c>
-      <c r="U42" s="13"/>
-      <c r="V42" s="13"/>
-      <c r="W42" s="13"/>
-      <c r="X42" s="13"/>
+      <c r="Y42" s="2"/>
+      <c r="Z42" s="2"/>
       <c r="AA42" s="11">
         <f t="shared" ref="AA42" si="45">SUM(AA32:AA41)</f>
         <v>1089.7689999999998</v>
@@ -5658,20 +5617,17 @@
         <f t="shared" ref="AB42" si="46">SUM(AB32:AB41)</f>
         <v>1312.8602000000001</v>
       </c>
-    </row>
-    <row r="43" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC42" s="14"/>
+    </row>
+    <row r="43" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="B43" s="4"/>
       <c r="C43" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
       <c r="G43" s="13">
         <v>0</v>
       </c>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
       <c r="K43" s="13">
         <v>0</v>
       </c>
@@ -5702,30 +5658,25 @@
       <c r="T43" s="13">
         <v>20</v>
       </c>
-      <c r="U43" s="13"/>
-      <c r="V43" s="13"/>
-      <c r="W43" s="13"/>
-      <c r="X43" s="13"/>
+      <c r="Y43" s="2"/>
+      <c r="Z43" s="2"/>
       <c r="AA43" s="13">
         <v>0</v>
       </c>
       <c r="AB43" s="13">
         <v>20</v>
       </c>
-    </row>
-    <row r="44" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC43" s="14"/>
+    </row>
+    <row r="44" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2"/>
+      <c r="B44" s="4"/>
       <c r="C44" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
       <c r="G44" s="13">
         <v>67.400000000000006</v>
       </c>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
       <c r="K44" s="13">
         <v>67.400000000000006</v>
       </c>
@@ -5756,30 +5707,25 @@
       <c r="T44" s="13">
         <v>47.9</v>
       </c>
-      <c r="U44" s="13"/>
-      <c r="V44" s="13"/>
-      <c r="W44" s="13"/>
-      <c r="X44" s="13"/>
+      <c r="Y44" s="2"/>
+      <c r="Z44" s="2"/>
       <c r="AA44" s="13">
         <v>67.400000000000006</v>
       </c>
       <c r="AB44" s="13">
         <v>47.9</v>
       </c>
-    </row>
-    <row r="45" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC44" s="14"/>
+    </row>
+    <row r="45" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="4"/>
       <c r="C45" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
       <c r="G45" s="13">
         <v>7.5</v>
       </c>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
       <c r="K45" s="13">
         <v>7.35</v>
       </c>
@@ -5810,30 +5756,25 @@
       <c r="T45" s="13">
         <v>5.5549999999999997</v>
       </c>
-      <c r="U45" s="13"/>
-      <c r="V45" s="13"/>
-      <c r="W45" s="13"/>
-      <c r="X45" s="13"/>
+      <c r="Y45" s="2"/>
+      <c r="Z45" s="2"/>
       <c r="AA45" s="13">
         <v>10</v>
       </c>
       <c r="AB45" s="13">
         <v>4.9859999999999998</v>
       </c>
-    </row>
-    <row r="46" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC45" s="14"/>
+    </row>
+    <row r="46" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="4"/>
       <c r="C46" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
       <c r="G46" s="13">
         <v>54.954999999999998</v>
       </c>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
       <c r="K46" s="13">
         <v>76.525000000000006</v>
       </c>
@@ -5864,18 +5805,19 @@
       <c r="T46" s="13">
         <v>122.59</v>
       </c>
-      <c r="U46" s="13"/>
-      <c r="V46" s="13"/>
-      <c r="W46" s="13"/>
-      <c r="X46" s="13"/>
+      <c r="Y46" s="2"/>
+      <c r="Z46" s="2"/>
       <c r="AA46" s="13">
         <v>138.578</v>
       </c>
       <c r="AB46" s="13">
         <v>115.498</v>
       </c>
-    </row>
-    <row r="47" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC46" s="14"/>
+    </row>
+    <row r="47" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2"/>
+      <c r="B47" s="4"/>
       <c r="C47" s="10" t="s">
         <v>75</v>
       </c>
@@ -5947,10 +5889,8 @@
         <f t="shared" si="48"/>
         <v>196.04500000000002</v>
       </c>
-      <c r="U47" s="13"/>
-      <c r="V47" s="13"/>
-      <c r="W47" s="13"/>
-      <c r="X47" s="13"/>
+      <c r="Y47" s="2"/>
+      <c r="Z47" s="2"/>
       <c r="AA47" s="23">
         <f t="shared" ref="AA47" si="49">SUM(AA43:AA46)</f>
         <v>215.97800000000001</v>
@@ -5959,20 +5899,17 @@
         <f t="shared" ref="AB47" si="50">SUM(AB43:AB46)</f>
         <v>188.38400000000001</v>
       </c>
-    </row>
-    <row r="48" spans="3:38" x14ac:dyDescent="0.25">
+      <c r="AC47" s="14"/>
+    </row>
+    <row r="48" spans="1:29" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="4"/>
       <c r="C48" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
       <c r="G48" s="13">
         <v>0</v>
       </c>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
       <c r="K48" s="13">
         <v>0</v>
       </c>
@@ -6003,30 +5940,26 @@
       <c r="T48" s="13">
         <v>14.648</v>
       </c>
-      <c r="U48" s="13"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="13"/>
-      <c r="X48" s="13"/>
+      <c r="Y48" s="2"/>
+      <c r="Z48" s="2"/>
       <c r="AA48" s="13">
         <v>20.684999999999999</v>
       </c>
       <c r="AB48" s="13">
         <v>15.561</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AC48" s="14"/>
+    </row>
+    <row r="49" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2"/>
+      <c r="B49" s="4"/>
       <c r="C49" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D49" s="23"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
       <c r="G49" s="13">
         <v>114.866</v>
       </c>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
       <c r="K49" s="13">
         <v>145.857</v>
       </c>
@@ -6057,30 +5990,25 @@
       <c r="T49" s="13">
         <v>273.54599999999999</v>
       </c>
-      <c r="U49" s="13"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
+      <c r="Y49" s="2"/>
+      <c r="Z49" s="2"/>
       <c r="AA49" s="13">
         <v>189.3</v>
       </c>
       <c r="AB49" s="13">
         <v>270.589</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AC49" s="14"/>
+    </row>
+    <row r="50" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2"/>
+      <c r="B50" s="4"/>
       <c r="C50" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
       <c r="G50" s="13">
         <v>17.114000000000001</v>
       </c>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
       <c r="K50" s="13">
         <v>14.116</v>
       </c>
@@ -6111,30 +6039,25 @@
       <c r="T50" s="13">
         <v>10.010999999999999</v>
       </c>
-      <c r="U50" s="13"/>
-      <c r="V50" s="13"/>
-      <c r="W50" s="13"/>
-      <c r="X50" s="13"/>
+      <c r="Y50" s="2"/>
+      <c r="Z50" s="2"/>
       <c r="AA50" s="13">
         <v>6.3</v>
       </c>
       <c r="AB50" s="13">
         <v>10.855</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AC50" s="14"/>
+    </row>
+    <row r="51" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2"/>
+      <c r="B51" s="4"/>
       <c r="C51" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
       <c r="G51" s="13">
         <v>16.100000000000001</v>
       </c>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
       <c r="K51" s="13">
         <v>5</v>
       </c>
@@ -6165,30 +6088,25 @@
       <c r="T51" s="13">
         <v>6.4619999999999997</v>
       </c>
-      <c r="U51" s="13"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
+      <c r="Y51" s="2"/>
+      <c r="Z51" s="2"/>
       <c r="AA51" s="13">
         <v>5.5</v>
       </c>
       <c r="AB51" s="13">
         <v>7</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AC51" s="14"/>
+    </row>
+    <row r="52" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2"/>
+      <c r="B52" s="4"/>
       <c r="C52" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
       <c r="G52" s="13">
         <v>9.327</v>
       </c>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
       <c r="K52" s="13">
         <v>22.731999999999999</v>
       </c>
@@ -6219,30 +6137,25 @@
       <c r="T52" s="13">
         <v>67.594999999999999</v>
       </c>
-      <c r="U52" s="13"/>
-      <c r="V52" s="13"/>
-      <c r="W52" s="13"/>
-      <c r="X52" s="13"/>
+      <c r="Y52" s="2"/>
+      <c r="Z52" s="2"/>
       <c r="AA52" s="13">
         <v>61.543999999999997</v>
       </c>
       <c r="AB52" s="13">
         <v>31.800999999999998</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AC52" s="14"/>
+    </row>
+    <row r="53" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2"/>
+      <c r="B53" s="4"/>
       <c r="C53" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
       <c r="G53" s="13">
         <v>187.92500000000001</v>
       </c>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
-      <c r="J53" s="13"/>
       <c r="K53" s="13">
         <v>315.435</v>
       </c>
@@ -6273,30 +6186,25 @@
       <c r="T53" s="13">
         <v>233.34899999999999</v>
       </c>
-      <c r="U53" s="13"/>
-      <c r="V53" s="13"/>
-      <c r="W53" s="13"/>
-      <c r="X53" s="13"/>
+      <c r="Y53" s="2"/>
+      <c r="Z53" s="2"/>
       <c r="AA53" s="13">
         <v>232.328</v>
       </c>
       <c r="AB53" s="13">
         <v>338.56</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AC53" s="14"/>
+    </row>
+    <row r="54" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2"/>
+      <c r="B54" s="4"/>
       <c r="C54" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
       <c r="G54" s="13">
         <v>1.4630000000000001</v>
       </c>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
       <c r="K54" s="13">
         <v>1.55</v>
       </c>
@@ -6327,30 +6235,25 @@
       <c r="T54" s="13">
         <v>11.55</v>
       </c>
-      <c r="U54" s="13"/>
-      <c r="V54" s="13"/>
-      <c r="W54" s="13"/>
-      <c r="X54" s="13"/>
+      <c r="Y54" s="2"/>
+      <c r="Z54" s="2"/>
       <c r="AA54" s="13">
         <v>21.9</v>
       </c>
       <c r="AB54" s="13">
         <v>5.806</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AC54" s="14"/>
+    </row>
+    <row r="55" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="4"/>
       <c r="C55" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
       <c r="G55" s="13">
         <v>52.433999999999997</v>
       </c>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
       <c r="K55" s="13">
         <v>72.334999999999994</v>
       </c>
@@ -6381,30 +6284,25 @@
       <c r="T55" s="13">
         <v>132.57499999999999</v>
       </c>
-      <c r="U55" s="13"/>
-      <c r="V55" s="13"/>
-      <c r="W55" s="13"/>
-      <c r="X55" s="13"/>
+      <c r="Y55" s="2"/>
+      <c r="Z55" s="2"/>
       <c r="AA55" s="13">
         <v>105.66800000000001</v>
       </c>
       <c r="AB55" s="13">
         <v>131.024</v>
       </c>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AC55" s="14"/>
+    </row>
+    <row r="56" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2"/>
+      <c r="B56" s="4"/>
       <c r="C56" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
       <c r="G56" s="13">
         <v>180.328</v>
       </c>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
       <c r="K56" s="13">
         <v>175.685</v>
       </c>
@@ -6435,30 +6333,25 @@
       <c r="T56" s="13">
         <v>256.166</v>
       </c>
-      <c r="U56" s="13"/>
-      <c r="V56" s="13"/>
-      <c r="W56" s="13"/>
-      <c r="X56" s="13"/>
+      <c r="Y56" s="2"/>
+      <c r="Z56" s="2"/>
       <c r="AA56" s="13">
         <v>211.28</v>
       </c>
       <c r="AB56" s="13">
         <v>273.01799999999997</v>
       </c>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AC56" s="14"/>
+    </row>
+    <row r="57" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+      <c r="B57" s="4"/>
       <c r="C57" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
       <c r="G57" s="13">
         <v>6.4</v>
       </c>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
       <c r="K57" s="13">
         <v>11.44</v>
       </c>
@@ -6489,30 +6382,25 @@
       <c r="T57" s="13">
         <v>3.0089999999999999</v>
       </c>
-      <c r="U57" s="13"/>
-      <c r="V57" s="13"/>
-      <c r="W57" s="13"/>
-      <c r="X57" s="13"/>
+      <c r="Y57" s="2"/>
+      <c r="Z57" s="2"/>
       <c r="AA57" s="13">
         <v>18.399999999999999</v>
       </c>
       <c r="AB57" s="13">
         <v>38.481999999999999</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AC57" s="14"/>
+    </row>
+    <row r="58" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+      <c r="B58" s="4"/>
       <c r="C58" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
       <c r="G58" s="13">
         <v>11</v>
       </c>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
       <c r="K58" s="13">
         <v>0</v>
       </c>
@@ -6543,10 +6431,6 @@
       <c r="T58" s="13">
         <v>0.754</v>
       </c>
-      <c r="U58" s="13"/>
-      <c r="V58" s="13"/>
-      <c r="W58" s="13"/>
-      <c r="X58" s="13"/>
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
       <c r="AA58" s="13">
@@ -6555,8 +6439,11 @@
       <c r="AB58" s="13">
         <v>0.754</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AC58" s="14"/>
+    </row>
+    <row r="59" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="B59" s="4"/>
       <c r="C59" s="10" t="s">
         <v>84</v>
       </c>
@@ -6628,10 +6515,8 @@
         <f t="shared" ref="T59" si="53">SUM(T48:T58)</f>
         <v>1009.6650000000001</v>
       </c>
-      <c r="U59" s="13"/>
-      <c r="V59" s="13"/>
-      <c r="W59" s="13"/>
-      <c r="X59" s="13"/>
+      <c r="Y59" s="2"/>
+      <c r="Z59" s="2"/>
       <c r="AA59" s="23">
         <f t="shared" ref="AA59" si="54">SUM(AA48:AA58)</f>
         <v>873.90499999999997</v>
@@ -6640,8 +6525,11 @@
         <f t="shared" ref="AB59" si="55">SUM(AB48:AB58)</f>
         <v>1123.4499999999998</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AC59" s="14"/>
+    </row>
+    <row r="60" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2"/>
+      <c r="B60" s="4"/>
       <c r="C60" s="1" t="s">
         <v>85</v>
       </c>
@@ -6716,7 +6604,8 @@
       <c r="U60" s="11"/>
       <c r="V60" s="11"/>
       <c r="W60" s="11"/>
-      <c r="X60" s="13"/>
+      <c r="Y60" s="2"/>
+      <c r="Z60" s="2"/>
       <c r="AA60" s="11">
         <f t="shared" ref="AA60" si="59">AA47+AA59</f>
         <v>1089.883</v>
@@ -6725,15 +6614,16 @@
         <f t="shared" ref="AB60" si="60">AB47+AB59</f>
         <v>1311.8339999999998</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AC60" s="14"/>
+    </row>
+    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="T61" s="13"/>
       <c r="U61" s="13"/>
       <c r="V61" s="13"/>
       <c r="W61" s="13"/>
       <c r="X61" s="13"/>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C62" s="1" t="s">
         <v>86</v>
       </c>
@@ -6762,7 +6652,7 @@
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C63" s="2" t="s">
         <v>87</v>
       </c>
@@ -6859,7 +6749,7 @@
       <c r="AE63" s="13"/>
       <c r="AF63" s="13"/>
     </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C64" s="2" t="s">
         <v>88</v>
       </c>
@@ -10123,170 +10013,170 @@
   <dimension ref="A3:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="10.83203125" style="50"/>
-    <col min="3" max="3" width="20" style="50" customWidth="1"/>
-    <col min="4" max="4" width="15" style="50" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" style="50" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="50"/>
-    <col min="7" max="7" width="13" style="50" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="50"/>
+    <col min="1" max="2" width="10.83203125" style="49"/>
+    <col min="3" max="3" width="20" style="49" customWidth="1"/>
+    <col min="4" max="4" width="15" style="49" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="49" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="49"/>
+    <col min="7" max="7" width="13" style="49" customWidth="1"/>
+    <col min="8" max="16384" width="10.83203125" style="49"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="49" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="51">
+      <c r="A4" s="50">
         <f>Modell!AC28</f>
         <v>155.97387000000001</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C6" s="52"/>
-      <c r="D6" s="52" t="s">
+      <c r="C6" s="51"/>
+      <c r="D6" s="51" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="51" t="s">
         <v>145</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="51" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="51" t="s">
         <v>146</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="51">
+        <v>136</v>
+      </c>
+      <c r="E7" s="51">
+        <v>6</v>
+      </c>
+      <c r="F7" s="54">
+        <f>D7*E7</f>
+        <v>816</v>
+      </c>
+      <c r="G7" s="54">
+        <f>F7/Modell!$B$5</f>
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C8" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="51">
+        <v>15</v>
+      </c>
+      <c r="E8" s="51">
+        <v>2</v>
+      </c>
+      <c r="F8" s="54">
+        <f t="shared" ref="F8:F9" si="0">D8*E8</f>
+        <v>30</v>
+      </c>
+      <c r="G8" s="54">
+        <f>F8/Modell!$B$5</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C9" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="E7" s="52">
-        <v>6</v>
-      </c>
-      <c r="F7" s="55">
-        <f>D7*E7</f>
-        <v>726</v>
-      </c>
-      <c r="G7" s="55">
-        <f>F7/Modell!$B$5</f>
-        <v>36.299999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C8" s="52" t="s">
-        <v>147</v>
-      </c>
-      <c r="D8" s="52">
-        <v>13</v>
-      </c>
-      <c r="E8" s="52">
-        <v>2</v>
-      </c>
-      <c r="F8" s="55">
-        <f t="shared" ref="F8:F9" si="0">D8*E8</f>
-        <v>26</v>
-      </c>
-      <c r="G8" s="55">
-        <f>F8/Modell!$B$5</f>
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C9" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="52">
+      <c r="D9" s="51">
         <v>5</v>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="51">
         <v>1</v>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="54">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="54">
         <f>F9/Modell!$B$5</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="56">
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="55">
         <f>SUM(F7:F9)</f>
-        <v>757</v>
-      </c>
-      <c r="G10" s="56">
+        <v>851</v>
+      </c>
+      <c r="G10" s="55">
         <f>SUM(G7:G9)</f>
-        <v>37.849999999999994</v>
+        <v>42.55</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="51" t="s">
         <v>152</v>
       </c>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="55">
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="54">
         <f>-Modell!B8</f>
         <v>-82.242999999999995</v>
       </c>
-      <c r="G12" s="55">
+      <c r="G12" s="54">
         <f>F12/Modell!B5</f>
         <v>-4.1121499999999997</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="55">
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="54">
         <f>Modell!B7</f>
         <v>32.676000000000002</v>
       </c>
-      <c r="G13" s="55">
+      <c r="G13" s="54">
         <f>F13/Modell!B5</f>
         <v>1.6338000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="52" t="s">
         <v>153</v>
       </c>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="56">
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="55">
         <f>SUM(F10:F13)</f>
-        <v>707.43300000000011</v>
-      </c>
-      <c r="G15" s="56">
+        <v>801.43300000000011</v>
+      </c>
+      <c r="G15" s="55">
         <f>SUM(G10:G13)</f>
-        <v>35.371649999999995</v>
+        <v>40.071649999999998</v>
       </c>
     </row>
   </sheetData>
@@ -10322,15 +10212,15 @@
       </c>
       <c r="D5" s="29">
         <f>Modell!$B$9/Modell!AC28</f>
-        <v>4.2415245579275549</v>
+        <v>4.6774950188772006</v>
       </c>
       <c r="E5" s="29">
         <f>Modell!$B$9/Modell!AD28</f>
-        <v>3.3418072274580735</v>
+        <v>3.6852991057820361</v>
       </c>
       <c r="F5" s="29">
         <f>Modell!$B$9/Modell!AE28</f>
-        <v>2.7342059133747871</v>
+        <v>3.0152447229125747</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -10339,15 +10229,15 @@
       </c>
       <c r="D6" s="29">
         <f>Modell!$B$9/Modell!AC11</f>
-        <v>4.9444838900141095</v>
+        <v>5.4527089141174274</v>
       </c>
       <c r="E6" s="29">
         <f>Modell!$B$9/Modell!AD11</f>
-        <v>3.6926270478329535</v>
+        <v>4.0721783846629958</v>
       </c>
       <c r="F6" s="29">
         <f>Modell!$B$9/Modell!AE11</f>
-        <v>2.860293586427177</v>
+        <v>3.1542924767543061</v>
       </c>
     </row>
     <row r="7" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -10356,15 +10246,15 @@
       </c>
       <c r="D7" s="29">
         <f>Modell!$B$4/Modell!AC18</f>
-        <v>6.7223789312735365</v>
+        <v>7.4693099236372626</v>
       </c>
       <c r="E7" s="29">
         <f>Modell!$B$4/Modell!AD18</f>
-        <v>4.8065172604233828</v>
+        <v>5.3405747338037584</v>
       </c>
       <c r="F7" s="29">
         <f>Modell!$B$4/Modell!AE18</f>
-        <v>3.620558125363031</v>
+        <v>4.0228423615144786</v>
       </c>
     </row>
   </sheetData>
@@ -10547,7 +10437,7 @@
     <row r="6" spans="1:145" x14ac:dyDescent="0.25">
       <c r="A6" s="22">
         <f>T24</f>
-        <v>-0.3519534329379409</v>
+        <v>-0.41675808964414679</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>45</v>
@@ -11987,7 +11877,7 @@
       </c>
       <c r="T24" s="22">
         <f>(T23-Modell!B4)/Modell!B4</f>
-        <v>-0.3519534329379409</v>
+        <v>-0.41675808964414679</v>
       </c>
     </row>
   </sheetData>
